--- a/reports/2025-12-15/category_report.xlsx
+++ b/reports/2025-12-15/category_report.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Category Report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,33 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9F4FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9EDF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +59,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,158 +459,231 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Qty</t>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Amount (Taxes Included)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Category Count</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Customers</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>BEER</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>2759.03</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>3172.87</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>245</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>165</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>COOLCIDER</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1486.81</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1709.88</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>184</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>223.9</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>223.9</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>868</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>RETAIL</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Rewards</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>-475</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>-475</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>-95</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>SPIRITS</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B7" s="3" t="n">
         <v>5870.72</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C7" s="3" t="n">
+        <v>6751.52</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>214</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>RETAIL</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>43.84</v>
-      </c>
-      <c r="C4" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="E7" s="3" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>WINE</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B8" s="3" t="n">
         <v>477.5</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C8" s="3" t="n">
+        <v>549.16</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>22</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="E8" s="3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>WINE RED</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>2682.43</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>3084.88</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>WINE WHITE</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B10" s="3" t="n">
         <v>1585.22</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C10" s="3" t="n">
+        <v>1823.03</v>
+      </c>
+      <c r="D10" s="3" t="n">
         <v>75</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WINE RED</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2682.43</v>
-      </c>
-      <c r="C7" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Rewards</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>-475</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-95</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>COOLCIDER</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1486.81</v>
-      </c>
-      <c r="C9" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>BEER</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2759.03</v>
-      </c>
-      <c r="C10" t="n">
-        <v>245</v>
+      <c r="E10" s="3" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>223.9</v>
-      </c>
-      <c r="C11" t="n">
-        <v>868</v>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>14654.45</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>16885.74</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1657</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>408</v>
       </c>
     </row>
   </sheetData>
